--- a/src/assets/employees/rafik.xlsx
+++ b/src/assets/employees/rafik.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,21 +427,241 @@
         <v>dev automatisme</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>additive clc_clsb</v>
       </c>
       <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v/>
+        <v>Préparation environnement de simulation programme CLSB ADDITIF</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>2026-09-01</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B3" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C3" t="str">
+        <v>additive clc_clsb</v>
+      </c>
+      <c r="D3" t="str">
+        <v>étude +recherche + modification</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2026-09-02</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B4" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C4" t="str">
+        <v>additive clc_clsb</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Etude programme LACTA CLC additif</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2026-09-03</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B5" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C5" t="str">
+        <v>additive clc_clsb</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Modif fonction comm additif</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B6" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C6" t="str">
+        <v>sonede</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Recherche sur aveva intouch 2014 v11.0</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2026-09-04</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B7" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C7" t="str">
+        <v>sms2i</v>
+      </c>
+      <c r="D7" t="str">
+        <v>rédaction rapport</v>
+      </c>
+      <c r="E7">
+        <v>12</v>
+      </c>
+      <c r="F7" t="str">
+        <v>2026-09-30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B8" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C8" t="str">
+        <v>intervention SAV</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Préparation architecture réseau NATILAIT</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8" t="str">
+        <v>2026-09-03</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B9" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C9" t="str">
+        <v>intervention SAV</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Intervention avec Mr khaled sur projet additif CLN</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2026-09-03</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B10" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C10" t="str">
+        <v>intervention SAV</v>
+      </c>
+      <c r="D10" t="str">
+        <v>intervention sur programme Additif CLN avec Mr khaled</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+      <c r="F10" t="str">
+        <v>2026-09-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B11" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C11" t="str">
+        <v>additive clc_clsb</v>
+      </c>
+      <c r="D11" t="str">
+        <v>etude programme CLC Lacta</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" t="str">
+        <v>2026-09-07</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B12" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C12" t="str">
+        <v>intervention SAV</v>
+      </c>
+      <c r="D12" t="str">
+        <v>intervention sur programme Additif CLN et clôture réserve du client avec mr Khaled</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12" t="str">
+        <v>2026-09-08</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B13" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C13" t="str">
+        <v>additive clc_clsb</v>
+      </c>
+      <c r="D13" t="str">
+        <v>etude des signaux programme LACTA CLC</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13" t="str">
+        <v>2026-09-09</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/assets/employees/rafik.xlsx
+++ b/src/assets/employees/rafik.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -656,12 +656,92 @@
         <v>3</v>
       </c>
       <c r="F13" t="str">
+        <v>2026-09-08</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B14" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C14" t="str">
+        <v>additive clc_clsb</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Modification programme pasto CLC pour l’ajout des signaux de comm avec l’additif</v>
+      </c>
+      <c r="E14">
+        <v>6</v>
+      </c>
+      <c r="F14" t="str">
         <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B15" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C15" t="str">
+        <v>additive clc_clsb</v>
+      </c>
+      <c r="D15" t="str">
+        <v>etude et modifie signaux de comm pasto CLC Additif</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15" t="str">
+        <v>2026-09-10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B16" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C16" t="str">
+        <v>additive clc_clsb</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Pointage et vérification matérielle elec additif</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16" t="str">
+        <v>2026-09-10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B17" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C17" t="str">
+        <v>sms2i</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Webinaire AVEVA 2026</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" t="str">
+        <v>2026-09-10</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F17"/>
   </ignoredErrors>
 </worksheet>
 </file>